--- a/release/v2026.5.2-rc.1/CodeSystem-mii-cs-pro-bdi-bdi2.xlsx
+++ b/release/v2026.5.2-rc.1/CodeSystem-mii-cs-pro-bdi-bdi2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T19:52:52+00:00</t>
+    <t>2026-07-27T20:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
